--- a/src/main/resources/i18n/common.xlsx
+++ b/src/main/resources/i18n/common.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Micro\CoreCommon\src\main\resources\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F306D9A-8FE5-4E39-BFEC-23E11A6A58EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04C7ED4-44F7-46C3-B608-1BCF3B9D117D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5265" yWindow="3030" windowWidth="21600" windowHeight="11460" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>key</t>
   </si>
@@ -102,6 +102,18 @@
   </si>
   <si>
     <t>翻訳できません: {0} {1}</t>
+  </si>
+  <si>
+    <t>LANGUAGE_CODE_NOT_SUPPORTED</t>
+  </si>
+  <si>
+    <t>Language code not supported</t>
+  </si>
+  <si>
+    <t>Mã ngôn ngữ không được hỗ trợ</t>
+  </si>
+  <si>
+    <t>言語コードはサポートされていません</t>
   </si>
 </sst>
 </file>
@@ -473,10 +485,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA4F4B4-AF50-4496-B9AC-762B42711D9F}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="55.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="62.5" bestFit="1" customWidth="1"/>
@@ -566,6 +578,20 @@
         <v>17</v>
       </c>
     </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/src/main/resources/i18n/common.xlsx
+++ b/src/main/resources/i18n/common.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Micro\CoreCommon\src\main\resources\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04C7ED4-44F7-46C3-B608-1BCF3B9D117D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA42BB32-0E34-441D-B6DC-E4A3256EEFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
+    <workbookView xWindow="33000" yWindow="2250" windowWidth="21600" windowHeight="11460" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>key</t>
   </si>
@@ -114,6 +114,18 @@
   </si>
   <si>
     <t>言語コードはサポートされていません</t>
+  </si>
+  <si>
+    <t>I18N_IMPORT_ERROR</t>
+  </si>
+  <si>
+    <t>Failed to import i18n file: {0}</t>
+  </si>
+  <si>
+    <t>Lỗi import file i18n: {0}</t>
+  </si>
+  <si>
+    <t>i18nファイルのインポートに失敗しました: {0}</t>
   </si>
 </sst>
 </file>
@@ -485,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA4F4B4-AF50-4496-B9AC-762B42711D9F}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.375" bestFit="1" customWidth="1"/>
@@ -592,6 +604,20 @@
         <v>25</v>
       </c>
     </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/src/main/resources/i18n/common.xlsx
+++ b/src/main/resources/i18n/common.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Micro\CoreCommon\src\main\resources\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA42BB32-0E34-441D-B6DC-E4A3256EEFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926D0BB6-CDCD-4F23-8E5C-8BAF607E90F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33000" yWindow="2250" windowWidth="21600" windowHeight="11460" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
+    <workbookView xWindow="36675" yWindow="3015" windowWidth="21600" windowHeight="11460" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
   <si>
     <t>key</t>
   </si>
@@ -126,6 +126,54 @@
   </si>
   <si>
     <t>i18nファイルのインポートに失敗しました: {0}</t>
+  </si>
+  <si>
+    <t>UNKNOWN</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>Không xác định</t>
+  </si>
+  <si>
+    <t>不明</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>Hoa Kỳ</t>
+  </si>
+  <si>
+    <t>アメリカ</t>
+  </si>
+  <si>
+    <t>VN</t>
+  </si>
+  <si>
+    <t>Vietnam</t>
+  </si>
+  <si>
+    <t>Việt Nam</t>
+  </si>
+  <si>
+    <t>ベトナム</t>
+  </si>
+  <si>
+    <t>JP</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>日本</t>
+  </si>
+  <si>
+    <t>Nhật Bản</t>
   </si>
 </sst>
 </file>
@@ -161,8 +209,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -497,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA4F4B4-AF50-4496-B9AC-762B42711D9F}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.375" bestFit="1" customWidth="1"/>
@@ -618,6 +669,65 @@
         <v>29</v>
       </c>
     </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C13" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/src/main/resources/i18n/common.xlsx
+++ b/src/main/resources/i18n/common.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Micro\CoreCommon\src\main\resources\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926D0BB6-CDCD-4F23-8E5C-8BAF607E90F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C96BD6-3768-44CD-8307-0FCDFAE343E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36675" yWindow="3015" windowWidth="21600" windowHeight="11460" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
+    <workbookView xWindow="29880" yWindow="4020" windowWidth="21600" windowHeight="11460" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -548,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA4F4B4-AF50-4496-B9AC-762B42711D9F}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.375" bestFit="1" customWidth="1"/>
@@ -725,9 +725,6 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="C13" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/src/main/resources/i18n/common.xlsx
+++ b/src/main/resources/i18n/common.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Micro\CoreCommon\src\main\resources\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C96BD6-3768-44CD-8307-0FCDFAE343E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15002FD7-A9D3-44E5-A75F-DED57805774A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29880" yWindow="4020" windowWidth="21600" windowHeight="11460" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
+    <workbookView xWindow="31080" yWindow="2295" windowWidth="21600" windowHeight="11460" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
   <si>
     <t>key</t>
   </si>
@@ -174,6 +174,18 @@
   </si>
   <si>
     <t>Nhật Bản</t>
+  </si>
+  <si>
+    <t>I18N_EXPORT_ERROR</t>
+  </si>
+  <si>
+    <t>Failed to export i18n file: {0}</t>
+  </si>
+  <si>
+    <t>Xuất file i18n thất bại: {0}</t>
+  </si>
+  <si>
+    <t>i18nファイルのエクスポートに失敗しました: {0}</t>
   </si>
 </sst>
 </file>
@@ -548,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA4F4B4-AF50-4496-B9AC-762B42711D9F}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.375" bestFit="1" customWidth="1"/>
@@ -671,57 +683,71 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>42</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>44</v>
       </c>
     </row>

--- a/src/main/resources/i18n/common.xlsx
+++ b/src/main/resources/i18n/common.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Micro\CoreCommon\src\main\resources\i18n\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Testing\Common\src\main\resources\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15002FD7-A9D3-44E5-A75F-DED57805774A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5383B5DF-F04A-48FC-9751-0AA398493223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31080" yWindow="2295" windowWidth="21600" windowHeight="11460" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
+    <workbookView xWindow="6495" yWindow="1710" windowWidth="21600" windowHeight="11460" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
   <si>
     <t>key</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>i18nファイルのエクスポートに失敗しました: {0}</t>
+  </si>
+  <si>
+    <t>is_error</t>
   </si>
 </sst>
 </file>
@@ -560,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA4F4B4-AF50-4496-B9AC-762B42711D9F}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.375" bestFit="1" customWidth="1"/>
@@ -569,7 +572,7 @@
     <col min="4" max="4" width="62.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -582,8 +585,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -596,8 +602,11 @@
       <c r="D2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -610,8 +619,11 @@
       <c r="D3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -624,8 +636,11 @@
       <c r="D4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -638,8 +653,11 @@
       <c r="D5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -652,8 +670,11 @@
       <c r="D6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -666,8 +687,11 @@
       <c r="D7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -680,8 +704,11 @@
       <c r="D8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>46</v>
       </c>
@@ -694,8 +721,11 @@
       <c r="D9" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -708,8 +738,11 @@
       <c r="D10" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -722,8 +755,11 @@
       <c r="D11" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -736,8 +772,11 @@
       <c r="D12" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>

--- a/src/main/resources/i18n/common.xlsx
+++ b/src/main/resources/i18n/common.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Testing\Common\src\main\resources\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5383B5DF-F04A-48FC-9751-0AA398493223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32F4A46-1BB1-4FE9-B54C-8D3857275608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6495" yWindow="1710" windowWidth="21600" windowHeight="11460" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
+    <workbookView xWindow="9630" yWindow="4830" windowWidth="20835" windowHeight="9420" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
   <si>
     <t>key</t>
   </si>
@@ -189,6 +189,18 @@
   </si>
   <si>
     <t>is_error</t>
+  </si>
+  <si>
+    <t>NOT_FOUND_COUNTRY</t>
+  </si>
+  <si>
+    <t>Không tìm thấy quốc gia</t>
+  </si>
+  <si>
+    <t>Country not found</t>
+  </si>
+  <si>
+    <t>国が見つかりません</t>
   </si>
 </sst>
 </file>
@@ -563,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA4F4B4-AF50-4496-B9AC-762B42711D9F}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.375" bestFit="1" customWidth="1"/>
@@ -789,6 +801,26 @@
       <c r="D13" t="s">
         <v>44</v>
       </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/resources/i18n/common.xlsx
+++ b/src/main/resources/i18n/common.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Testing\Common\src\main\resources\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32F4A46-1BB1-4FE9-B54C-8D3857275608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CB6A51-97F5-4331-B38C-5CFCB7B00EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9630" yWindow="4830" windowWidth="20835" windowHeight="9420" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
+    <workbookView xWindow="34020" yWindow="3480" windowWidth="20835" windowHeight="9420" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
   <si>
     <t>key</t>
   </si>
@@ -201,6 +201,30 @@
   </si>
   <si>
     <t>国が見つかりません</t>
+  </si>
+  <si>
+    <t>ルール実行エラー、原因：{0}</t>
+  </si>
+  <si>
+    <t>Lỗi khi thực thi rule, nguyên nhân: {0}</t>
+  </si>
+  <si>
+    <t>Rule executes error cause by {0}</t>
+  </si>
+  <si>
+    <t>DROOL_EXECUTION_ERROR</t>
+  </si>
+  <si>
+    <t>ルールファイルが生成されていません</t>
+  </si>
+  <si>
+    <t>Chưa sinh file quy tắc</t>
+  </si>
+  <si>
+    <t>Rule file not generated</t>
+  </si>
+  <si>
+    <t>DROOL_NOT_GENERATED</t>
   </si>
 </sst>
 </file>
@@ -575,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA4F4B4-AF50-4496-B9AC-762B42711D9F}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.375" bestFit="1" customWidth="1"/>
@@ -822,6 +846,40 @@
         <v>1</v>
       </c>
     </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/src/main/resources/i18n/common.xlsx
+++ b/src/main/resources/i18n/common.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Testing\Common\src\main\resources\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CB6A51-97F5-4331-B38C-5CFCB7B00EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05224E4E-0150-4CC5-B7FC-EE552A62F2AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34020" yWindow="3480" windowWidth="20835" windowHeight="9420" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
+    <workbookView xWindow="33345" yWindow="1485" windowWidth="20835" windowHeight="9420" activeTab="1" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Department" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="191">
   <si>
     <t>key</t>
   </si>
@@ -225,6 +226,390 @@
   </si>
   <si>
     <t>DROOL_NOT_GENERATED</t>
+  </si>
+  <si>
+    <t>CANNOT_BE_NULL</t>
+  </si>
+  <si>
+    <t>{0} không được để trống</t>
+  </si>
+  <si>
+    <t>{0} cannot be null</t>
+  </si>
+  <si>
+    <t>{0} をヌルにすることはできません</t>
+  </si>
+  <si>
+    <t>BK915SGQ</t>
+  </si>
+  <si>
+    <t>Bac Ninh Branch</t>
+  </si>
+  <si>
+    <t>Chi nhánh Bắc Ninh</t>
+  </si>
+  <si>
+    <t>Bac Ninh支店</t>
+  </si>
+  <si>
+    <t>JG1020GK</t>
+  </si>
+  <si>
+    <t>Ho Chi Minh Processing Center</t>
+  </si>
+  <si>
+    <t>Trung tâm khai thác Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>Ho Chi Minh取扱センター</t>
+  </si>
+  <si>
+    <t>HK28JS21</t>
+  </si>
+  <si>
+    <t>Hai Phong Warehouse</t>
+  </si>
+  <si>
+    <t>Kho hàng Hải Phòng</t>
+  </si>
+  <si>
+    <t>Hai Phong倉庫</t>
+  </si>
+  <si>
+    <t>ZN93JQPL</t>
+  </si>
+  <si>
+    <t>Ha Tinh Station</t>
+  </si>
+  <si>
+    <t>Trạm Hà Tĩnh</t>
+  </si>
+  <si>
+    <t>Ha Tinhステーション</t>
+  </si>
+  <si>
+    <t>TK84LPSS</t>
+  </si>
+  <si>
+    <t>Vung Tau Warehouse</t>
+  </si>
+  <si>
+    <t>Kho hàng Vũng Tàu</t>
+  </si>
+  <si>
+    <t>Vung Tau倉庫</t>
+  </si>
+  <si>
+    <t>FKSKJJVI</t>
+  </si>
+  <si>
+    <t>Thanh Hoa Processing Center</t>
+  </si>
+  <si>
+    <t>Trung tâm khai thác Thanh Hóa</t>
+  </si>
+  <si>
+    <t>Thanh Hoa取扱センター</t>
+  </si>
+  <si>
+    <t>DL72MKOP</t>
+  </si>
+  <si>
+    <t>Long An Processing Center</t>
+  </si>
+  <si>
+    <t>Trung tâm khai thác Long An</t>
+  </si>
+  <si>
+    <t>Long An取扱センター</t>
+  </si>
+  <si>
+    <t>QP12ZBXA</t>
+  </si>
+  <si>
+    <t>Vung Tau Station</t>
+  </si>
+  <si>
+    <t>Trạm Vũng Tàu</t>
+  </si>
+  <si>
+    <t>Vung Tauステーション</t>
+  </si>
+  <si>
+    <t>VN99TYQC</t>
+  </si>
+  <si>
+    <t>Long An Post Office</t>
+  </si>
+  <si>
+    <t>Bưu cục Long An</t>
+  </si>
+  <si>
+    <t>Long An郵便局</t>
+  </si>
+  <si>
+    <t>HT45CXQP</t>
+  </si>
+  <si>
+    <t>Can Tho Branch</t>
+  </si>
+  <si>
+    <t>Chi nhánh Cần Thơ</t>
+  </si>
+  <si>
+    <t>Can Tho支店</t>
+  </si>
+  <si>
+    <t>LP32ADKL</t>
+  </si>
+  <si>
+    <t>Can Tho Station</t>
+  </si>
+  <si>
+    <t>Trạm Cần Thơ</t>
+  </si>
+  <si>
+    <t>Can Thoステーション</t>
+  </si>
+  <si>
+    <t>ZX19TRMN</t>
+  </si>
+  <si>
+    <t>PL08YWQE</t>
+  </si>
+  <si>
+    <t>JN73QVSK</t>
+  </si>
+  <si>
+    <t>Hue Transaction Point</t>
+  </si>
+  <si>
+    <t>Điểm giao dịch Huế</t>
+  </si>
+  <si>
+    <t>Hue取引所</t>
+  </si>
+  <si>
+    <t>DL09MNXT</t>
+  </si>
+  <si>
+    <t>Lam Đong Branch</t>
+  </si>
+  <si>
+    <t>Chi nhánh Lâm Đồng</t>
+  </si>
+  <si>
+    <t>Lam Đong支店</t>
+  </si>
+  <si>
+    <t>LD82PQOS</t>
+  </si>
+  <si>
+    <t>Ha Tinh Branch</t>
+  </si>
+  <si>
+    <t>Chi nhánh Hà Tĩnh</t>
+  </si>
+  <si>
+    <t>Ha Tinh支店</t>
+  </si>
+  <si>
+    <t>KT55LKJD</t>
+  </si>
+  <si>
+    <t>Thai Nguyen Warehouse</t>
+  </si>
+  <si>
+    <t>Kho hàng Thái Nguyên</t>
+  </si>
+  <si>
+    <t>Thai Nguyen倉庫</t>
+  </si>
+  <si>
+    <t>GL12SDQW</t>
+  </si>
+  <si>
+    <t>Can Tho Transaction Point</t>
+  </si>
+  <si>
+    <t>Điểm giao dịch Cần Thơ</t>
+  </si>
+  <si>
+    <t>Can Tho取引所</t>
+  </si>
+  <si>
+    <t>HN11ASDF</t>
+  </si>
+  <si>
+    <t>Long An Branch</t>
+  </si>
+  <si>
+    <t>Chi nhánh Long An</t>
+  </si>
+  <si>
+    <t>Long An支店</t>
+  </si>
+  <si>
+    <t>TB22LKQW</t>
+  </si>
+  <si>
+    <t>Hai Phong Transaction Point</t>
+  </si>
+  <si>
+    <t>Điểm giao dịch Hải Phòng</t>
+  </si>
+  <si>
+    <t>Hai Phong取引所</t>
+  </si>
+  <si>
+    <t>BN33ZXCJ</t>
+  </si>
+  <si>
+    <t>Thai Nguyen Transaction Point</t>
+  </si>
+  <si>
+    <t>Điểm giao dịch Thái Nguyên</t>
+  </si>
+  <si>
+    <t>Thai Nguyen取引所</t>
+  </si>
+  <si>
+    <t>BG44OPAS</t>
+  </si>
+  <si>
+    <t>Long An Warehouse</t>
+  </si>
+  <si>
+    <t>Kho hàng Long An</t>
+  </si>
+  <si>
+    <t>Long An倉庫</t>
+  </si>
+  <si>
+    <t>QN55QWER</t>
+  </si>
+  <si>
+    <t>CT12LOPQ</t>
+  </si>
+  <si>
+    <t>DT23ZNBV</t>
+  </si>
+  <si>
+    <t>VL34MXSA</t>
+  </si>
+  <si>
+    <t>Quang Ninh Station</t>
+  </si>
+  <si>
+    <t>Trạm Quảng Ninh</t>
+  </si>
+  <si>
+    <t>Quang Ninhステーション</t>
+  </si>
+  <si>
+    <t>BT45PQWE</t>
+  </si>
+  <si>
+    <t>Long An Transaction Point</t>
+  </si>
+  <si>
+    <t>Điểm giao dịch Long An</t>
+  </si>
+  <si>
+    <t>Long An取引所</t>
+  </si>
+  <si>
+    <t>LA56ASDQ</t>
+  </si>
+  <si>
+    <t>NT45KLMN</t>
+  </si>
+  <si>
+    <t>Ha Noi Station</t>
+  </si>
+  <si>
+    <t>Trạm Hà Nội</t>
+  </si>
+  <si>
+    <t>Ha Noiステーション</t>
+  </si>
+  <si>
+    <t>BP56ZXCQ</t>
+  </si>
+  <si>
+    <t>Kien Giang Warehouse</t>
+  </si>
+  <si>
+    <t>Kho hàng Kiên Giang</t>
+  </si>
+  <si>
+    <t>Kien Giang倉庫</t>
+  </si>
+  <si>
+    <t>QB67ASDF</t>
+  </si>
+  <si>
+    <t>Nghe An Post Office</t>
+  </si>
+  <si>
+    <t>Bưu cục Nghệ An</t>
+  </si>
+  <si>
+    <t>Nghe An郵便局</t>
+  </si>
+  <si>
+    <t>QH78PLMN</t>
+  </si>
+  <si>
+    <t>Phu Tho Post Office</t>
+  </si>
+  <si>
+    <t>Bưu cục Phú Thọ</t>
+  </si>
+  <si>
+    <t>Phu Tho郵便局</t>
+  </si>
+  <si>
+    <t>DN89QWER</t>
+  </si>
+  <si>
+    <t>Kien Giang Processing Center</t>
+  </si>
+  <si>
+    <t>Trung tâm khai thác Kiên Giang</t>
+  </si>
+  <si>
+    <t>Kien Giang取扱センター</t>
+  </si>
+  <si>
+    <t>INT001</t>
+  </si>
+  <si>
+    <t>Phu Tho Transaction Point</t>
+  </si>
+  <si>
+    <t>Điểm giao dịch Phú Thọ</t>
+  </si>
+  <si>
+    <t>Phu Tho取引所</t>
+  </si>
+  <si>
+    <t>INT002</t>
+  </si>
+  <si>
+    <t>Ha Noi Transaction Point</t>
+  </si>
+  <si>
+    <t>Điểm giao dịch Hà Nội</t>
+  </si>
+  <si>
+    <t>Ha Noi取引所</t>
+  </si>
+  <si>
+    <t>INT003</t>
+  </si>
+  <si>
+    <t>INT004</t>
   </si>
 </sst>
 </file>
@@ -599,7 +984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA4F4B4-AF50-4496-B9AC-762B42711D9F}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.375" bestFit="1" customWidth="1"/>
@@ -880,8 +1265,681 @@
         <v>1</v>
       </c>
     </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727DB7D4-84DB-4EB9-86D9-01ED1B7A76BE}">
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" t="s">
+        <v>116</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>117</v>
+      </c>
+      <c r="B16" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D16" t="s">
+        <v>120</v>
+      </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17" t="s">
+        <v>124</v>
+      </c>
+      <c r="E17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>125</v>
+      </c>
+      <c r="B18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" t="s">
+        <v>135</v>
+      </c>
+      <c r="D20" t="s">
+        <v>136</v>
+      </c>
+      <c r="E20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" t="s">
+        <v>139</v>
+      </c>
+      <c r="D21" t="s">
+        <v>140</v>
+      </c>
+      <c r="E21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" t="s">
+        <v>144</v>
+      </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C23" t="s">
+        <v>147</v>
+      </c>
+      <c r="D23" t="s">
+        <v>148</v>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>149</v>
+      </c>
+      <c r="B24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" t="s">
+        <v>139</v>
+      </c>
+      <c r="D24" t="s">
+        <v>140</v>
+      </c>
+      <c r="E24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>150</v>
+      </c>
+      <c r="B25" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" t="s">
+        <v>140</v>
+      </c>
+      <c r="E25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>151</v>
+      </c>
+      <c r="B26" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" t="s">
+        <v>110</v>
+      </c>
+      <c r="E26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>152</v>
+      </c>
+      <c r="B27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C27" t="s">
+        <v>154</v>
+      </c>
+      <c r="D27" t="s">
+        <v>155</v>
+      </c>
+      <c r="E27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>156</v>
+      </c>
+      <c r="B28" t="s">
+        <v>157</v>
+      </c>
+      <c r="C28" t="s">
+        <v>158</v>
+      </c>
+      <c r="D28" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>160</v>
+      </c>
+      <c r="B29" t="s">
+        <v>130</v>
+      </c>
+      <c r="C29" t="s">
+        <v>131</v>
+      </c>
+      <c r="D29" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>161</v>
+      </c>
+      <c r="B30" t="s">
+        <v>162</v>
+      </c>
+      <c r="C30" t="s">
+        <v>163</v>
+      </c>
+      <c r="D30" t="s">
+        <v>164</v>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>165</v>
+      </c>
+      <c r="B31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C31" t="s">
+        <v>167</v>
+      </c>
+      <c r="D31" t="s">
+        <v>168</v>
+      </c>
+      <c r="E31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>169</v>
+      </c>
+      <c r="B32" t="s">
+        <v>170</v>
+      </c>
+      <c r="C32" t="s">
+        <v>171</v>
+      </c>
+      <c r="D32" t="s">
+        <v>172</v>
+      </c>
+      <c r="E32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>173</v>
+      </c>
+      <c r="B33" t="s">
+        <v>174</v>
+      </c>
+      <c r="C33" t="s">
+        <v>175</v>
+      </c>
+      <c r="D33" t="s">
+        <v>176</v>
+      </c>
+      <c r="E33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>177</v>
+      </c>
+      <c r="B34" t="s">
+        <v>178</v>
+      </c>
+      <c r="C34" t="s">
+        <v>179</v>
+      </c>
+      <c r="D34" t="s">
+        <v>180</v>
+      </c>
+      <c r="E34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>181</v>
+      </c>
+      <c r="B35" t="s">
+        <v>182</v>
+      </c>
+      <c r="C35" t="s">
+        <v>183</v>
+      </c>
+      <c r="D35" t="s">
+        <v>184</v>
+      </c>
+      <c r="E35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>185</v>
+      </c>
+      <c r="B36" t="s">
+        <v>186</v>
+      </c>
+      <c r="C36" t="s">
+        <v>187</v>
+      </c>
+      <c r="D36" t="s">
+        <v>188</v>
+      </c>
+      <c r="E36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>189</v>
+      </c>
+      <c r="B37" t="s">
+        <v>146</v>
+      </c>
+      <c r="C37" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" t="s">
+        <v>148</v>
+      </c>
+      <c r="E37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>190</v>
+      </c>
+      <c r="B38" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" t="s">
+        <v>82</v>
+      </c>
+      <c r="E38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/i18n/common.xlsx
+++ b/src/main/resources/i18n/common.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Testing\Common\src\main\resources\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05224E4E-0150-4CC5-B7FC-EE552A62F2AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128C18AC-F667-489F-A9BC-21B89478C79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33345" yWindow="1485" windowWidth="20835" windowHeight="9420" activeTab="1" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="194">
   <si>
     <t>key</t>
   </si>
@@ -610,6 +610,15 @@
   </si>
   <si>
     <t>INT004</t>
+  </si>
+  <si>
+    <t>KS92039</t>
+  </si>
+  <si>
+    <t>Test Department</t>
+  </si>
+  <si>
+    <t>Bưu cục test</t>
   </si>
 </sst>
 </file>
@@ -1290,8 +1299,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727DB7D4-84DB-4EB9-86D9-01ED1B7A76BE}">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="27.75" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1939,7 +1951,25 @@
         <v>0</v>
       </c>
     </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>191</v>
+      </c>
+      <c r="B39" t="s">
+        <v>192</v>
+      </c>
+      <c r="C39" t="s">
+        <v>193</v>
+      </c>
+      <c r="D39" t="s">
+        <v>192</v>
+      </c>
+      <c r="E39" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/main/resources/i18n/common.xlsx
+++ b/src/main/resources/i18n/common.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Testing\Common\src\main\resources\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128C18AC-F667-489F-A9BC-21B89478C79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EE3439-468F-47E9-9916-6EE64954AF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33345" yWindow="1485" windowWidth="20835" windowHeight="9420" activeTab="1" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
+    <workbookView xWindow="33345" yWindow="1485" windowWidth="20835" windowHeight="9420" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="198">
   <si>
     <t>key</t>
   </si>
@@ -619,6 +619,18 @@
   </si>
   <si>
     <t>Bưu cục test</t>
+  </si>
+  <si>
+    <t>MUST_BE_LIST</t>
+  </si>
+  <si>
+    <t>Nguồn dữ liệu (from) phải là danh sách (List), nhưng nhận được: {0}</t>
+  </si>
+  <si>
+    <t>The source data (from) must be a List, but received: {0}</t>
+  </si>
+  <si>
+    <t>データソース (from) はリストでなければなりませんが、受け取ったのは {0} です。</t>
   </si>
 </sst>
 </file>
@@ -993,12 +1005,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA4F4B4-AF50-4496-B9AC-762B42711D9F}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="55.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="62.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1288,6 +1300,23 @@
         <v>66</v>
       </c>
       <c r="E17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>194</v>
+      </c>
+      <c r="B18" t="s">
+        <v>196</v>
+      </c>
+      <c r="C18" t="s">
+        <v>195</v>
+      </c>
+      <c r="D18" t="s">
+        <v>197</v>
+      </c>
+      <c r="E18" t="b">
         <v>1</v>
       </c>
     </row>

--- a/src/main/resources/i18n/common.xlsx
+++ b/src/main/resources/i18n/common.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Intellj\Testing\Common\src\main\resources\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EE3439-468F-47E9-9916-6EE64954AF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88D1AE0-E466-4B15-8B1E-F4B375790D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33345" yWindow="1485" windowWidth="20835" windowHeight="9420" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
+    <workbookView xWindow="37200" yWindow="1725" windowWidth="20835" windowHeight="9420" activeTab="1" xr2:uid="{E50E03D4-4F8A-4BB7-9FDA-052AF5257747}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="206">
   <si>
     <t>key</t>
   </si>
@@ -631,6 +631,30 @@
   </si>
   <si>
     <t>データソース (from) はリストでなければなりませんが、受け取ったのは {0} です。</t>
+  </si>
+  <si>
+    <t>タンチ郵便局</t>
+  </si>
+  <si>
+    <t>Bưu cục Thanh Trì</t>
+  </si>
+  <si>
+    <t>Thanh Tri Post Office</t>
+  </si>
+  <si>
+    <t>TTR01</t>
+  </si>
+  <si>
+    <t>情報技術センター</t>
+  </si>
+  <si>
+    <t>Trung tâm công nghệ</t>
+  </si>
+  <si>
+    <t>Information Technology Center</t>
+  </si>
+  <si>
+    <t>TTCN</t>
   </si>
 </sst>
 </file>
@@ -1328,7 +1352,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727DB7D4-84DB-4EB9-86D9-01ED1B7A76BE}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="27.75" bestFit="1" customWidth="1"/>
@@ -1997,6 +2021,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>205</v>
+      </c>
+      <c r="B40" t="s">
+        <v>204</v>
+      </c>
+      <c r="C40" t="s">
+        <v>203</v>
+      </c>
+      <c r="D40" t="s">
+        <v>202</v>
+      </c>
+      <c r="E40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>201</v>
+      </c>
+      <c r="B41" t="s">
+        <v>200</v>
+      </c>
+      <c r="C41" t="s">
+        <v>199</v>
+      </c>
+      <c r="D41" t="s">
+        <v>198</v>
+      </c>
+      <c r="E41" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
